--- a/data/availability/projects/city-edge-developments/jade-park-al-maqsad.xlsx
+++ b/data/availability/projects/city-edge-developments/jade-park-al-maqsad.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for jade-park-al-maqsad</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -909,7 +919,6 @@
       <c r="G2" t="n">
         <v>75</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -966,7 +975,6 @@
       <c r="G3" t="n">
         <v>178</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1023,7 +1031,6 @@
       <c r="G4" t="n">
         <v>218</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1080,7 +1087,6 @@
       <c r="G5" t="n">
         <v>284</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1137,7 +1143,6 @@
       <c r="G6" t="n">
         <v>246</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1194,7 +1199,6 @@
       <c r="G7" t="n">
         <v>380</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1251,7 +1255,6 @@
       <c r="G8" t="n">
         <v>588</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1308,7 +1311,6 @@
       <c r="G9" t="n">
         <v>692</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>

--- a/data/availability/projects/city-edge-developments/jade-park-al-maqsad.xlsx
+++ b/data/availability/projects/city-edge-developments/jade-park-al-maqsad.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
